--- a/SWASH.xlsx
+++ b/SWASH.xlsx
@@ -64,7 +64,7 @@
     <t>20136451</t>
   </si>
   <si>
-    <t>NSCAFE AMERICANO 10S</t>
+    <t>NESCAFE AMRCN 10X2 G</t>
   </si>
   <si>
     <t>5</t>

--- a/SWASH.xlsx
+++ b/SWASH.xlsx
@@ -19,7 +19,7 @@
     <t>20046081</t>
   </si>
   <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
+    <t>G/DAY MOCCA 10x20 G</t>
   </si>
   <si>
     <t>SWASH</t>
